--- a/membership_forms/022_gym_membership_form_with_paypal_integration--membership_forms.xlsx
+++ b/membership_forms/022_gym_membership_form_with_paypal_integration--membership_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -839,8 +839,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -868,12 +868,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'monthly_membership',_'label':_'monthly_membership'}</t>
+          <t>monthly_membership</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly Membership', 'label': 'Monthly Membership'}</t>
+          <t>Monthly Membership</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'yearly_membership',_'label':_'yearly_membership'}</t>
+          <t>yearly_membership</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Yearly Membership', 'label': 'Yearly Membership'}</t>
+          <t>Yearly Membership</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'monthly_plus',_'label':_'monthly_plus'}</t>
+          <t>monthly_plus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly Plus', 'label': 'Monthly Plus'}</t>
+          <t>Monthly Plus</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'paypal',_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'PayPal', 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Bank Transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'cash',_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Cash', 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'paypal',_'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'PayPal', 'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Bank Transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'cash',_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Cash', 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
